--- a/testData/TestData.xlsx
+++ b/testData/TestData.xlsx
@@ -1,9 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{1284DD8F-672B-4CFE-BD4F-2AD71D3AB3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2475090\eclipse-workspace\EaseMyTripProject\testData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{B5AAE96A-06AE-4E4F-B6BB-541CB1E63401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{FBFBF966-5D29-4139-A097-15676D1A9C2C}"/>
   </bookViews>
@@ -11,7 +16,6 @@
     <sheet name="EaseMyTrip" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -21,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
   <si>
     <t>Status</t>
   </si>
@@ -74,19 +78,22 @@
     <t>Manali</t>
   </si>
   <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Email address is required and it should be valid.</t>
+  </si>
+  <si>
     <t>12</t>
   </si>
   <si>
-    <t>PASS</t>
-  </si>
-  <si>
     <t>9909</t>
   </si>
   <si>
-    <t>Email address is required and it should be valid.</t>
-  </si>
-  <si>
     <t>10022</t>
+  </si>
+  <si>
+    <t>37646</t>
   </si>
 </sst>
 </file>
@@ -524,10 +531,10 @@
         <v>6</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -545,13 +552,13 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -569,10 +576,10 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
